--- a/src/documents/fixtures/tiny.xlsx
+++ b/src/documents/fixtures/tiny.xlsx
@@ -12,9 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>פריט</t>
+  </si>
+  <si>
+    <t>כמות</t>
   </si>
   <si>
     <t>מחיר</t>
@@ -420,17 +423,19 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1"/>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -445,7 +450,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -456,18 +461,16 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B4"/>
       <c r="C4">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A4:B4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -481,7 +484,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
